--- a/artfynd/A 17074-2022 artfynd.xlsx
+++ b/artfynd/A 17074-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127505253</v>
       </c>
       <c r="B2" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>127505251</v>
       </c>
       <c r="B3" t="n">
-        <v>98470</v>
+        <v>98471</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17074-2022 artfynd.xlsx
+++ b/artfynd/A 17074-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127505253</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>127505251</v>
       </c>
       <c r="B3" t="n">
-        <v>98471</v>
+        <v>98473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17074-2022 artfynd.xlsx
+++ b/artfynd/A 17074-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127505253</v>
       </c>
       <c r="B2" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>127505251</v>
       </c>
       <c r="B3" t="n">
-        <v>98473</v>
+        <v>98479</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17074-2022 artfynd.xlsx
+++ b/artfynd/A 17074-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127505253</v>
       </c>
       <c r="B2" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>127505251</v>
       </c>
       <c r="B3" t="n">
-        <v>98479</v>
+        <v>98482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17074-2022 artfynd.xlsx
+++ b/artfynd/A 17074-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127505253</v>
       </c>
       <c r="B2" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>127505251</v>
       </c>
       <c r="B3" t="n">
-        <v>98482</v>
+        <v>98490</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17074-2022 artfynd.xlsx
+++ b/artfynd/A 17074-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127505253</v>
       </c>
       <c r="B2" t="n">
-        <v>98384</v>
+        <v>98385</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>127505251</v>
       </c>
       <c r="B3" t="n">
-        <v>98490</v>
+        <v>98491</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17074-2022 artfynd.xlsx
+++ b/artfynd/A 17074-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127505253</v>
       </c>
       <c r="B2" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>127505251</v>
       </c>
       <c r="B3" t="n">
-        <v>98491</v>
+        <v>98492</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17074-2022 artfynd.xlsx
+++ b/artfynd/A 17074-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127505253</v>
       </c>
       <c r="B2" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>127505251</v>
       </c>
       <c r="B3" t="n">
-        <v>98492</v>
+        <v>98493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
